--- a/data/yrendon.xlsx
+++ b/data/yrendon.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d3c7c81f20a53ce1/Documentos/FIFI/Resumen/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d3c7c81f20a53ce1/Documentos/FIFI/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{C3F1DE41-FC59-46DA-9712-317A108CA597}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21132878-774C-49E4-B474-AD492857520E}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{C3F1DE41-FC59-46DA-9712-317A108CA597}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{428B6B89-E066-47D7-9925-46363B595A83}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{7A27F12D-6F9D-4758-B7D5-03B08667753E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="16">
   <si>
     <t>INV13</t>
   </si>
@@ -84,15 +84,6 @@
   </si>
   <si>
     <t>Beneficio en %</t>
-  </si>
-  <si>
-    <t>INV14</t>
-  </si>
-  <si>
-    <t>INV15</t>
-  </si>
-  <si>
-    <t>INV16</t>
   </si>
 </sst>
 </file>
@@ -482,7 +473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EEB1E01-21BC-442C-965D-94DEC222FAE4}">
-  <dimension ref="A1:N46"/>
+  <dimension ref="A1:N50"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
@@ -2421,7 +2412,7 @@
         <v>45817</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>1</v>
@@ -2467,7 +2458,7 @@
         <v>45847</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>1</v>
@@ -2513,18 +2504,21 @@
         <v>45878</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D46" s="3">
-        <f t="shared" ref="D46" si="91">+D45++E45+K45</f>
+        <f t="shared" ref="D46:D50" si="91">+D45++E45+K45</f>
         <v>7790.04</v>
+      </c>
+      <c r="G46" s="2">
+        <v>109.06</v>
       </c>
       <c r="H46" s="4">
         <f t="shared" si="84"/>
-        <v>4790.04</v>
+        <v>4899.1000000000004</v>
       </c>
       <c r="I46" s="4">
         <f t="shared" si="85"/>
@@ -2536,18 +2530,199 @@
       </c>
       <c r="K46" s="4">
         <f t="shared" si="87"/>
-        <v>0</v>
+        <v>109.06</v>
       </c>
       <c r="L46" s="4">
         <f t="shared" si="88"/>
-        <v>4790.04</v>
+        <v>4899.1000000000004</v>
       </c>
       <c r="M46" s="4">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>3.6353333333333335</v>
       </c>
       <c r="N46" s="5">
         <f t="shared" si="90"/>
+        <v>1.3999928113334463E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A47" s="1">
+        <v>45909</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D47" s="3">
+        <f t="shared" si="91"/>
+        <v>7899.1</v>
+      </c>
+      <c r="G47" s="2">
+        <v>181.68</v>
+      </c>
+      <c r="H47" s="4">
+        <f t="shared" ref="H47:H50" si="92">+H46+G47</f>
+        <v>5080.7800000000007</v>
+      </c>
+      <c r="I47" s="4">
+        <f t="shared" ref="I47:I50" si="93">+G47*0</f>
+        <v>0</v>
+      </c>
+      <c r="J47" s="4">
+        <f t="shared" ref="J47:J50" si="94">+J46+I47</f>
+        <v>0</v>
+      </c>
+      <c r="K47" s="4">
+        <f t="shared" ref="K47:K50" si="95">+G47-I47</f>
+        <v>181.68</v>
+      </c>
+      <c r="L47" s="4">
+        <f t="shared" ref="L47:L50" si="96">+L46+K47</f>
+        <v>5080.7800000000007</v>
+      </c>
+      <c r="M47" s="4">
+        <f t="shared" ref="M47:M50" si="97">+K47/30</f>
+        <v>6.056</v>
+      </c>
+      <c r="N47" s="5">
+        <f t="shared" ref="N47:N50" si="98">+G47/D47</f>
+        <v>2.3000088617690623E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A48" s="1">
+        <v>45939</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D48" s="3">
+        <f t="shared" si="91"/>
+        <v>8080.7800000000007</v>
+      </c>
+      <c r="G48" s="2">
+        <v>169.7</v>
+      </c>
+      <c r="H48" s="4">
+        <f t="shared" si="92"/>
+        <v>5250.4800000000005</v>
+      </c>
+      <c r="I48" s="4">
+        <f t="shared" si="93"/>
+        <v>0</v>
+      </c>
+      <c r="J48" s="4">
+        <f t="shared" si="94"/>
+        <v>0</v>
+      </c>
+      <c r="K48" s="4">
+        <f t="shared" si="95"/>
+        <v>169.7</v>
+      </c>
+      <c r="L48" s="4">
+        <f t="shared" si="96"/>
+        <v>5250.4800000000005</v>
+      </c>
+      <c r="M48" s="4">
+        <f t="shared" si="97"/>
+        <v>5.6566666666666663</v>
+      </c>
+      <c r="N48" s="5">
+        <f t="shared" si="98"/>
+        <v>2.1000447976556716E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A49" s="1">
+        <v>45970</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D49" s="3">
+        <f t="shared" si="91"/>
+        <v>8250.4800000000014</v>
+      </c>
+      <c r="G49" s="2">
+        <v>297.01</v>
+      </c>
+      <c r="H49" s="4">
+        <f t="shared" si="92"/>
+        <v>5547.4900000000007</v>
+      </c>
+      <c r="I49" s="4">
+        <f t="shared" si="93"/>
+        <v>0</v>
+      </c>
+      <c r="J49" s="4">
+        <f t="shared" si="94"/>
+        <v>0</v>
+      </c>
+      <c r="K49" s="4">
+        <f t="shared" si="95"/>
+        <v>297.01</v>
+      </c>
+      <c r="L49" s="4">
+        <f t="shared" si="96"/>
+        <v>5547.4900000000007</v>
+      </c>
+      <c r="M49" s="4">
+        <f t="shared" si="97"/>
+        <v>9.9003333333333323</v>
+      </c>
+      <c r="N49" s="5">
+        <f t="shared" si="98"/>
+        <v>3.599911762709563E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A50" s="1">
+        <v>46000</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D50" s="3">
+        <f t="shared" si="91"/>
+        <v>8547.4900000000016</v>
+      </c>
+      <c r="H50" s="4">
+        <f t="shared" si="92"/>
+        <v>5547.4900000000007</v>
+      </c>
+      <c r="I50" s="4">
+        <f t="shared" si="93"/>
+        <v>0</v>
+      </c>
+      <c r="J50" s="4">
+        <f t="shared" si="94"/>
+        <v>0</v>
+      </c>
+      <c r="K50" s="4">
+        <f t="shared" si="95"/>
+        <v>0</v>
+      </c>
+      <c r="L50" s="4">
+        <f t="shared" si="96"/>
+        <v>5547.4900000000007</v>
+      </c>
+      <c r="M50" s="4">
+        <f t="shared" si="97"/>
+        <v>0</v>
+      </c>
+      <c r="N50" s="5">
+        <f t="shared" si="98"/>
         <v>0</v>
       </c>
     </row>

--- a/data/yrendon.xlsx
+++ b/data/yrendon.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\OneDrive\Documentos\Proyectos\FIFI\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d3c7c81f20a53ce1/Documentos/Proyectos/FIFI/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{221ED903-BABB-4044-9079-CF96BFA06080}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{221ED903-BABB-4044-9079-CF96BFA06080}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3AC98FEE-10D9-410B-9D18-DB534E643502}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{7A27F12D-6F9D-4758-B7D5-03B08667753E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="16">
   <si>
     <t>INV13</t>
   </si>
@@ -473,7 +473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EEB1E01-21BC-442C-965D-94DEC222FAE4}">
-  <dimension ref="A1:N53"/>
+  <dimension ref="A1:N56"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
@@ -2835,9 +2835,12 @@
         <f t="shared" si="99"/>
         <v>9030.5000000000018</v>
       </c>
+      <c r="G53" s="2">
+        <v>115.99</v>
+      </c>
       <c r="H53" s="4">
         <f t="shared" si="100"/>
-        <v>6030.5000000000009</v>
+        <v>6146.4900000000007</v>
       </c>
       <c r="I53" s="4">
         <f t="shared" si="101"/>
@@ -2849,19 +2852,157 @@
       </c>
       <c r="K53" s="4">
         <f t="shared" si="103"/>
-        <v>0</v>
+        <v>115.99</v>
       </c>
       <c r="L53" s="4">
         <f t="shared" si="104"/>
-        <v>6030.5000000000009</v>
+        <v>6146.4900000000007</v>
       </c>
       <c r="M53" s="4">
         <f t="shared" si="105"/>
-        <v>0</v>
+        <v>3.866333333333333</v>
       </c>
       <c r="N53" s="5">
         <f t="shared" si="106"/>
-        <v>0</v>
+        <v>1.2844250041525937E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A54" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D54" s="3">
+        <f t="shared" ref="D54:D56" si="107">+D53++E53+K53</f>
+        <v>9146.4900000000016</v>
+      </c>
+      <c r="G54" s="2">
+        <v>60.85</v>
+      </c>
+      <c r="H54" s="4">
+        <f t="shared" ref="H54:H56" si="108">+H53+G54</f>
+        <v>6207.3400000000011</v>
+      </c>
+      <c r="I54" s="4">
+        <f t="shared" ref="I54:I56" si="109">+G54*0</f>
+        <v>0</v>
+      </c>
+      <c r="J54" s="4">
+        <f t="shared" ref="J54:J56" si="110">+J53+I54</f>
+        <v>0</v>
+      </c>
+      <c r="K54" s="4">
+        <f t="shared" ref="K54:K56" si="111">+G54-I54</f>
+        <v>60.85</v>
+      </c>
+      <c r="L54" s="4">
+        <f t="shared" ref="L54:L56" si="112">+L53+K54</f>
+        <v>6207.3400000000011</v>
+      </c>
+      <c r="M54" s="4">
+        <f t="shared" ref="M54:M56" si="113">+K54/30</f>
+        <v>2.0283333333333333</v>
+      </c>
+      <c r="N54" s="5">
+        <f t="shared" ref="N54:N56" si="114">+G54/D54</f>
+        <v>6.6528252914505991E-3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A55" s="1">
+        <v>46151</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D55" s="3">
+        <f t="shared" si="107"/>
+        <v>9207.340000000002</v>
+      </c>
+      <c r="G55" s="2">
+        <v>218.34</v>
+      </c>
+      <c r="H55" s="4">
+        <f t="shared" si="108"/>
+        <v>6425.6800000000012</v>
+      </c>
+      <c r="I55" s="4">
+        <f t="shared" si="109"/>
+        <v>0</v>
+      </c>
+      <c r="J55" s="4">
+        <f t="shared" si="110"/>
+        <v>0</v>
+      </c>
+      <c r="K55" s="4">
+        <f t="shared" si="111"/>
+        <v>218.34</v>
+      </c>
+      <c r="L55" s="4">
+        <f t="shared" si="112"/>
+        <v>6425.6800000000012</v>
+      </c>
+      <c r="M55" s="4">
+        <f t="shared" si="113"/>
+        <v>7.2780000000000005</v>
+      </c>
+      <c r="N55" s="5">
+        <f t="shared" si="114"/>
+        <v>2.3713689295714067E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A56" s="1">
+        <v>46182</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D56" s="3">
+        <f t="shared" si="107"/>
+        <v>9425.6800000000021</v>
+      </c>
+      <c r="G56" s="2">
+        <v>130.55000000000001</v>
+      </c>
+      <c r="H56" s="4">
+        <f t="shared" si="108"/>
+        <v>6556.2300000000014</v>
+      </c>
+      <c r="I56" s="4">
+        <f t="shared" si="109"/>
+        <v>0</v>
+      </c>
+      <c r="J56" s="4">
+        <f t="shared" si="110"/>
+        <v>0</v>
+      </c>
+      <c r="K56" s="4">
+        <f t="shared" si="111"/>
+        <v>130.55000000000001</v>
+      </c>
+      <c r="L56" s="4">
+        <f t="shared" si="112"/>
+        <v>6556.2300000000014</v>
+      </c>
+      <c r="M56" s="4">
+        <f t="shared" si="113"/>
+        <v>4.3516666666666675</v>
+      </c>
+      <c r="N56" s="5">
+        <f t="shared" si="114"/>
+        <v>1.3850459595488069E-2</v>
       </c>
     </row>
   </sheetData>
